--- a/sizes.xlsx
+++ b/sizes.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DESKTOP\schMatrixes\RGBMatrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F104EAF7-5FFD-404D-BB8A-CE91B3CBAB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{3909CA40-1A41-4FCA-9D25-B0BA736B69AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" xr2:uid="{559C0B81-8BCB-491B-870A-D4F3BFA0BCE1}"/>
+    <workbookView xWindow="14835" yWindow="0" windowWidth="10215" windowHeight="17385" xr2:uid="{559C0B81-8BCB-491B-870A-D4F3BFA0BCE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>single window</t>
   </si>
@@ -59,6 +60,99 @@
   </si>
   <si>
     <t>single led</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>real</t>
+  </si>
+  <si>
+    <t>used</t>
+  </si>
+  <si>
+    <t>whole height</t>
+  </si>
+  <si>
+    <t>kicsi</t>
+  </si>
+  <si>
+    <t>nagy</t>
+  </si>
+  <si>
+    <t>fekvő</t>
+  </si>
+  <si>
+    <t>álló</t>
+  </si>
+  <si>
+    <t>arány</t>
+  </si>
+  <si>
+    <t>tanuló szélesség:</t>
+  </si>
+  <si>
+    <t>konyhák+tanulók szélesség:</t>
+  </si>
+  <si>
+    <t>szoknya mélység:</t>
+  </si>
+  <si>
+    <t>konyhák+tanulók magasság:</t>
+  </si>
+  <si>
+    <t>mátrix panel szélesség</t>
+  </si>
+  <si>
+    <t>mátrix panel magasság:</t>
+  </si>
+  <si>
+    <t>tanuló mélység:</t>
+  </si>
+  <si>
+    <t>3 panel</t>
+  </si>
+  <si>
+    <t>2 panel</t>
+  </si>
+  <si>
+    <t>konyha mélység:</t>
+  </si>
+  <si>
+    <t>oldalanként szoknya szélesség:</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>megjegyzés</t>
+  </si>
+  <si>
+    <t>használt</t>
+  </si>
+  <si>
+    <t>oldalpanel szélesség:</t>
+  </si>
+  <si>
+    <t>oldalpanel magasság:</t>
+  </si>
+  <si>
+    <t>szoknya magassága:</t>
+  </si>
+  <si>
+    <t>shift:</t>
+  </si>
+  <si>
+    <t>dollar</t>
+  </si>
+  <si>
+    <t>db</t>
+  </si>
+  <si>
+    <t>ösz</t>
+  </si>
+  <si>
+    <t>HSS</t>
   </si>
 </sst>
 </file>
@@ -82,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -90,15 +184,104 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,126 +598,694 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C5FEB92-1EC6-4CDC-BE9B-680791E2B7A8}">
-  <dimension ref="A3:E18"/>
+  <dimension ref="A3:I61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
         <v>1.6</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <f>1.2</f>
         <v>1.2</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.4</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.6</v>
       </c>
-      <c r="E4">
-        <f>2*B4+C4</f>
+      <c r="F4">
+        <f>2*C4+D4</f>
         <v>2.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="G4">
+        <f>8*(F4+E4)</f>
+        <v>27.2</v>
+      </c>
+      <c r="H4">
+        <f>13*C4+12*B4</f>
+        <v>34.800000000000004</v>
+      </c>
+      <c r="I4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <f>B4*$C5/$C4</f>
+        <v>1.3333333333333335</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <f>D4*$C5/$C4</f>
+        <v>0.33333333333333337</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:F5" si="0">E4*$C5/$C4</f>
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <f>2*C5+D5</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="G5">
+        <f>8*(F5+E5)</f>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="H5">
+        <f>13*C5+12*B5</f>
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <f>I4*$C5/$C4</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>1.3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0.3</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <f>2*C6+D6</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G6">
+        <f>8*(F6+E6)</f>
+        <v>22.4</v>
+      </c>
+      <c r="H6">
+        <f>13*C6+12*B6</f>
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>5</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
         <v>6</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C15">
-        <f>($B$10/$B$4)</f>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <f>($C$10/$C$4)</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="D15">
-        <f>($B$10*2.2/$B$4)</f>
-        <v>1.8333333333333335</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="B16">
-        <f>8*(E4+D4)</f>
+      <c r="C16">
+        <f>8*(F4+E4)</f>
         <v>27.2</v>
       </c>
-      <c r="C16">
-        <f t="shared" ref="C16:D18" si="0">$B16*C$15</f>
+      <c r="D16">
+        <f>$C16*D$15</f>
         <v>22.666666666666668</v>
       </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>49.866666666666667</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="B17">
-        <f>13*B4+12*A4</f>
+      <c r="C17">
+        <f>13*C4+12*B4</f>
         <v>34.800000000000004</v>
       </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
+      <c r="D17">
+        <f>$C17*D$15</f>
         <v>29.000000000000004</v>
       </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>63.800000000000011</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C18" s="1">
         <v>60</v>
       </c>
-      <c r="C18">
-        <f t="shared" si="0"/>
+      <c r="D18">
+        <f>$C18*D$15</f>
         <v>50</v>
       </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>110.00000000000001</v>
+      <c r="I18">
+        <f>2*(1.5+2.2+0.8)+3.2</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I19">
+        <f>12.2/15.8</f>
+        <v>0.77215189873417711</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I20">
+        <f>20.6/28.6</f>
+        <v>0.72027972027972031</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22">
+        <v>20.6</v>
+      </c>
+      <c r="G22">
+        <v>12.2</v>
+      </c>
+      <c r="H22">
+        <f>F22/G22</f>
+        <v>1.6885245901639347</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>26.6</v>
+      </c>
+      <c r="G23">
+        <v>15.8</v>
+      </c>
+      <c r="H23">
+        <f>F23/G23</f>
+        <v>1.6835443037974684</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f>F22/F23</f>
+        <v>0.77443609022556392</v>
+      </c>
+      <c r="G24">
+        <f>G22/G23</f>
+        <v>0.77215189873417711</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <f>F23/F22</f>
+        <v>1.29126213592233</v>
+      </c>
+      <c r="G25">
+        <f t="shared" ref="G25:H25" si="1">G23/G22</f>
+        <v>1.2950819672131149</v>
+      </c>
+      <c r="H25">
+        <f>(H22+H23)/2</f>
+        <v>1.6860344469807016</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1</v>
+      </c>
+      <c r="G28" s="6">
+        <f>G29/F29</f>
+        <v>1.1407766990291262</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="5">
+        <v>20.6</v>
+      </c>
+      <c r="G29" s="6">
+        <v>23.5</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="5">
+        <v>3</v>
+      </c>
+      <c r="G30" s="6">
+        <f>F30*G$28</f>
+        <v>3.4223300970873787</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="5">
+        <v>2.9</v>
+      </c>
+      <c r="G31" s="6">
+        <f t="shared" ref="G31:G50" si="2">F31*G$28</f>
+        <v>3.3082524271844655</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="5">
+        <v>10.6</v>
+      </c>
+      <c r="G32" s="6">
+        <f t="shared" si="2"/>
+        <v>12.092233009708737</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="5">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="G33" s="6">
+        <f t="shared" si="2"/>
+        <v>40.155339805825243</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <f>29.5*1000/22.4</f>
+        <v>1316.9642857142858</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="5">
+        <v>45.5</v>
+      </c>
+      <c r="G34" s="6">
+        <f t="shared" si="2"/>
+        <v>51.905339805825243</v>
+      </c>
+      <c r="H34" s="6" t="str">
+        <f>"-1.6mm nyál miatt"</f>
+        <v>-1.6mm nyál miatt</v>
+      </c>
+      <c r="I34" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" t="str">
+        <f>"1:1317"</f>
+        <v>1:1317</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="5">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G35" s="6">
+        <f t="shared" si="2"/>
+        <v>5.2475728155339798</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E36" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="G36" s="6">
+        <f t="shared" si="2"/>
+        <v>3.0800970873786406</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E37" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="5">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G37" s="6">
+        <f t="shared" si="2"/>
+        <v>11.635922330097086</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E38" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" s="5">
+        <v>20.2</v>
+      </c>
+      <c r="G38" s="6">
+        <f>F38*G$28</f>
+        <v>23.043689320388346</v>
+      </c>
+      <c r="H38" s="6" t="str">
+        <f>"-3.2mm nyák miatt"</f>
+        <v>-3.2mm nyák miatt</v>
+      </c>
+      <c r="I38" s="7">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E39" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="5">
+        <v>45.5</v>
+      </c>
+      <c r="G39" s="6">
+        <f t="shared" si="2"/>
+        <v>51.905339805825243</v>
+      </c>
+      <c r="H39" s="6" t="str">
+        <f>"-1.6mm nyák miatt"</f>
+        <v>-1.6mm nyák miatt</v>
+      </c>
+      <c r="I39" s="7">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E40" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="5">
+        <v>8.4</v>
+      </c>
+      <c r="G40" s="6">
+        <f t="shared" si="2"/>
+        <v>9.5825242718446599</v>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" s="7">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="6"/>
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="9"/>
+      <c r="I50" s="10"/>
+    </row>
+    <row r="59" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <v>45.39</v>
+      </c>
+    </row>
+    <row r="60" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <f>(C59+C61)/2</f>
+        <v>46.66</v>
+      </c>
+    </row>
+    <row r="61" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <v>47.93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FF7C49-9A49-44B0-BB08-A8E52E6C6596}">
+  <dimension ref="C1:F3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2">
+        <v>0.4</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <f>D2*E2</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <f>D3*E3</f>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/sizes.xlsx
+++ b/sizes.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DESKTOP\schMatrixes\RGBMatrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{3909CA40-1A41-4FCA-9D25-B0BA736B69AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C7F869-78D7-4F41-99FF-FB7DE4CA94EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14835" yWindow="0" windowWidth="10215" windowHeight="17385" xr2:uid="{559C0B81-8BCB-491B-870A-D4F3BFA0BCE1}"/>
+    <workbookView xWindow="-16305" yWindow="-5400" windowWidth="16410" windowHeight="10170" xr2:uid="{559C0B81-8BCB-491B-870A-D4F3BFA0BCE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -686,7 +685,7 @@
         <v>0.33333333333333337</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:F5" si="0">E4*$C5/$C4</f>
+        <f t="shared" ref="E5" si="0">E4*$C5/$C4</f>
         <v>0.5</v>
       </c>
       <c r="F5">
@@ -869,7 +868,7 @@
         <v>1.29126213592233</v>
       </c>
       <c r="G25">
-        <f t="shared" ref="G25:H25" si="1">G23/G22</f>
+        <f t="shared" ref="G25" si="1">G23/G22</f>
         <v>1.2950819672131149</v>
       </c>
       <c r="H25">
@@ -1220,6 +1219,22 @@
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="10"/>
+    </row>
+    <row r="52" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <f>(20.3-6*0.3)</f>
+        <v>18.5</v>
+      </c>
+      <c r="D52">
+        <f>C52/7.2</f>
+        <v>2.5694444444444442</v>
+      </c>
+    </row>
+    <row r="53" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="E53">
+        <f>2.5*7+0.3*6</f>
+        <v>19.3</v>
+      </c>
     </row>
     <row r="59" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C59">
